--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487026_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487026_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. KANDULU</t>
+          <t>A. MEANA PEREZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1724</v>
+        <v>2.813</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9382</v>
+        <v>4.2325</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2342</v>
+        <v>-1.4194</v>
       </c>
       <c r="G2" t="n">
-        <v>1.3697</v>
+        <v>1.5716</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.717</v>
+        <v>-1.7776</v>
       </c>
       <c r="I2" t="n">
-        <v>2.0867</v>
+        <v>3.3492</v>
       </c>
       <c r="J2" t="n">
-        <v>1.3453</v>
+        <v>2.6998</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0034</v>
+        <v>-1.3913</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3418</v>
+        <v>4.091</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0244</v>
+        <v>-1.1281</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7204</v>
+        <v>-0.3863</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7449</v>
+        <v>-0.7418</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.2321</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q2" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8214</v>
+        <v>1.6427</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3982</v>
+        <v>-0.7052</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4678</v>
+        <v>-0.19</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.5152</v>
       </c>
       <c r="V2" t="n">
-        <v>1.6366</v>
+        <v>2.3573</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1786</v>
+        <v>3.7761</v>
       </c>
       <c r="X2" t="n">
-        <v>0.4579</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. ENABULELE OGUNSUYI</t>
+          <t>D. KANDULU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2902</v>
+        <v>2.4774</v>
       </c>
       <c r="E3" t="n">
-        <v>4.469</v>
+        <v>1.5397</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.1787</v>
+        <v>0.9378</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3873</v>
+        <v>1.3697</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3421</v>
+        <v>-0.717</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9549</v>
+        <v>2.0867</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9148</v>
+        <v>1.3453</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7569</v>
+        <v>0.0034</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1579</v>
+        <v>1.3418</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.5275</v>
+        <v>0.0244</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4148</v>
+        <v>-0.7204</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.1127</v>
+        <v>0.7449</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q3" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0534</v>
+        <v>0.8214</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2521</v>
+        <v>0.7032</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5378</v>
+        <v>1.0692</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2858</v>
+        <v>-0.366</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3491</v>
+        <v>1.6366</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0698</v>
+        <v>1.1786</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.4189</v>
+        <v>0.4579</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MEANA PEREZ</t>
+          <t>J. PALAMOS MOLINS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0808</v>
+        <v>1.1418</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5003</v>
+        <v>-0.9767</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4194</v>
+        <v>2.1186</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5716</v>
+        <v>1.1238</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.7776</v>
+        <v>-0.4154</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3492</v>
+        <v>1.5392</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6998</v>
+        <v>2.0803</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.3913</v>
+        <v>1.0546</v>
       </c>
       <c r="L4" t="n">
-        <v>4.091</v>
+        <v>1.0257</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1281</v>
+        <v>-0.9566</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3863</v>
+        <v>-1.47</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7418</v>
+        <v>0.5134</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4107</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6427</v>
+        <v>1.8481</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4374</v>
+        <v>0.094</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9222</v>
+        <v>0.0231</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5152</v>
+        <v>0.0709</v>
       </c>
       <c r="V4" t="n">
-        <v>2.3573</v>
+        <v>1.1561</v>
       </c>
       <c r="W4" t="n">
-        <v>3.7761</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.4189</v>
+        <v>1.1561</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. PALAMOS MOLINS</t>
+          <t>M. ENABULELE OGUNSUYI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7472</v>
+        <v>0.8851</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5196</v>
+        <v>3.0045</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2668</v>
+        <v>-2.1194</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1238</v>
+        <v>1.3873</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4154</v>
+        <v>2.3421</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5392</v>
+        <v>-0.9549</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0803</v>
+        <v>3.9148</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0546</v>
+        <v>3.7569</v>
       </c>
       <c r="L5" t="n">
-        <v>1.0257</v>
+        <v>0.1579</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9566</v>
+        <v>-2.5275</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.47</v>
+        <v>-1.4148</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5134</v>
+        <v>-1.1127</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.2321</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.0801</v>
+        <v>-2.0534</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8481</v>
+        <v>2.0534</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6994</v>
+        <v>-0.1531</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4802</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2192</v>
+        <v>-0.2265</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1561</v>
+        <v>-0.3491</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0698</v>
       </c>
       <c r="X5" t="n">
-        <v>1.1561</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1196</v>
+        <v>0.6175</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5869</v>
+        <v>1.1758</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7065</v>
+        <v>-0.5583</v>
       </c>
       <c r="G6" t="n">
         <v>1.0261</v>
@@ -922,13 +922,13 @@
         <v>2.0534</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9938</v>
+        <v>-0.2567</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.651</v>
+        <v>-0.0621</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3428</v>
+        <v>-0.1946</v>
       </c>
       <c r="V6" t="n">
         <v>-1.1786</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.122</v>
+        <v>-0.9127999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1265</v>
+        <v>0.3357</v>
       </c>
       <c r="F7" t="n">
         <v>-1.2485</v>
@@ -1000,10 +1000,10 @@
         <v>0.616</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0813</v>
+        <v>0.1279</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1704</v>
+        <v>0.3796</v>
       </c>
       <c r="U7" t="n">
         <v>-0.2517</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.665</v>
+        <v>-2.0471</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2115</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4535</v>
+        <v>-1.4831</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7765</v>
@@ -1078,13 +1078,13 @@
         <v>0.4107</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1197</v>
+        <v>-0.2625</v>
       </c>
       <c r="T8" t="n">
-        <v>0.368</v>
+        <v>0.0155</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2483</v>
+        <v>-0.2779</v>
       </c>
       <c r="V8" t="n">
         <v>-1.4189</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5889</v>
+        <v>-2.1112</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4065</v>
+        <v>-1.9881</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1824</v>
+        <v>-0.1231</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8338</v>
@@ -1156,13 +1156,13 @@
         <v>1.2321</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7818000000000001</v>
+        <v>-0.3042</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6587</v>
+        <v>-0.2403</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1231</v>
+        <v>-0.0638</v>
       </c>
       <c r="V9" t="n">
         <v>-1.1786</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9019</v>
+        <v>-3.229</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2785</v>
+        <v>-1.5462</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6235</v>
+        <v>-1.6828</v>
       </c>
       <c r="G10" t="n">
         <v>-5.3045</v>
@@ -1234,13 +1234,13 @@
         <v>1.4374</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2134</v>
+        <v>-0.5405</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9881</v>
+        <v>-0.2559</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2254</v>
+        <v>-0.2846</v>
       </c>
       <c r="V10" t="n">
         <v>1.1786</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2866</v>
+        <v>-3.3766</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3384</v>
+        <v>-2.6062</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9482</v>
+        <v>-0.7704</v>
       </c>
       <c r="G11" t="n">
         <v>-0.5679999999999999</v>
@@ -1312,13 +1312,13 @@
         <v>1.8481</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8767</v>
+        <v>-0.9666</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1121</v>
+        <v>-0.3799</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7645999999999999</v>
+        <v>-0.5868</v>
       </c>
       <c r="V11" t="n">
         <v>-1.6366</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4642</v>
+        <v>-3.7864</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8222</v>
+        <v>-1.2333</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6421</v>
+        <v>-2.5531</v>
       </c>
       <c r="G12" t="n">
         <v>-2.0749</v>
@@ -1390,13 +1390,13 @@
         <v>0.4107</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.533</v>
+        <v>-0.8552</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5192</v>
+        <v>0.0696</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0138</v>
+        <v>-0.9249000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2402</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.857599999999998</v>
+        <v>-7.528300000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0442</v>
+        <v>1.3737</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.901800000000001</v>
+        <v>-8.901700000000002</v>
       </c>
       <c r="G13" t="n">
         <v>-4.7359</v>
@@ -1444,7 +1444,7 @@
         <v>7.779599999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>5.9403</v>
+        <v>5.940299999999999</v>
       </c>
       <c r="L13" t="n">
         <v>1.8392</v>
@@ -1468,13 +1468,13 @@
         <v>14.374</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.448</v>
+        <v>-3.1189</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1728999999999999</v>
+        <v>0.5022</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.621</v>
+        <v>-3.6211</v>
       </c>
       <c r="V13" t="n">
         <v>0.3266000000000002</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. GARCIA CARRERO</t>
+          <t>R. FABREGA URPINA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.3369</v>
+        <v>8.099</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7677</v>
+        <v>8.847899999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>4.5692</v>
+        <v>-0.7489</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8184</v>
+        <v>9.3171</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0287</v>
+        <v>4.2628</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7897</v>
+        <v>5.0543</v>
       </c>
       <c r="J14" t="n">
-        <v>1.7167</v>
+        <v>10.2238</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4405</v>
+        <v>4.8699</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2763</v>
+        <v>5.3539</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8984</v>
+        <v>-0.9067</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.4118</v>
+        <v>-0.6071</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5134</v>
+        <v>-0.2996</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2588</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2588</v>
+        <v>1.8481</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8553</v>
+        <v>0.3835</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5465</v>
+        <v>0.3059</v>
       </c>
       <c r="U14" t="n">
-        <v>2.4018</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>3.4045</v>
+        <v>-1.3963</v>
       </c>
       <c r="W14" t="n">
-        <v>2.5975</v>
+        <v>0.3716</v>
       </c>
       <c r="X14" t="n">
-        <v>0.8070000000000001</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. FABREGA URPINA</t>
+          <t>P. GARCIA CARRERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.4365</v>
+        <v>7.7544</v>
       </c>
       <c r="E15" t="n">
-        <v>8.3249</v>
+        <v>4.2908</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8884</v>
+        <v>3.4637</v>
       </c>
       <c r="G15" t="n">
-        <v>9.3171</v>
+        <v>0.8184</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2628</v>
+        <v>0.0287</v>
       </c>
       <c r="I15" t="n">
-        <v>5.0543</v>
+        <v>0.7897</v>
       </c>
       <c r="J15" t="n">
-        <v>10.2238</v>
+        <v>1.7167</v>
       </c>
       <c r="K15" t="n">
-        <v>4.8699</v>
+        <v>1.4405</v>
       </c>
       <c r="L15" t="n">
-        <v>5.3539</v>
+        <v>0.2763</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9067</v>
+        <v>-0.8984</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6071</v>
+        <v>-1.4118</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2996</v>
+        <v>0.5134</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2053</v>
+        <v>2.2588</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8481</v>
+        <v>2.2588</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2789</v>
+        <v>1.2728</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2171</v>
+        <v>-0.0235</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0618</v>
+        <v>1.2963</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.3963</v>
+        <v>3.4045</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3716</v>
+        <v>2.5975</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.7679</v>
+        <v>0.8070000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. TAMAYO LESMES</t>
+          <t>F. STUTZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,40 +1657,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8218</v>
+        <v>3.3133</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3911</v>
+        <v>3.1028</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5693</v>
+        <v>0.2105</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8731</v>
+        <v>2.7383</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3203</v>
+        <v>0.9861</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4472</v>
+        <v>1.7522</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1159</v>
+        <v>2.6534</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.655</v>
+        <v>1.4828</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5391</v>
+        <v>1.1706</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7572</v>
+        <v>0.0849</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6653</v>
+        <v>-0.4967</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.092</v>
+        <v>0.5816</v>
       </c>
       <c r="P16" t="n">
         <v>0.8214</v>
@@ -1702,28 +1702,28 @@
         <v>0.8214</v>
       </c>
       <c r="S16" t="n">
-        <v>1.9351</v>
+        <v>0.1027</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3283</v>
+        <v>-0.0311</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3932</v>
+        <v>0.1338</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9384</v>
+        <v>-0.3491</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1786</v>
+        <v>0.4805</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2402</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. STUTZ</t>
+          <t>A. TAMAYO LESMES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2707</v>
+        <v>1.645</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4751</v>
+        <v>1.9266</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2045</v>
+        <v>-0.2816</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7383</v>
+        <v>-0.8731</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9861</v>
+        <v>-1.3203</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7522</v>
+        <v>0.4472</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6534</v>
+        <v>-0.1159</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4828</v>
+        <v>-0.655</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1706</v>
+        <v>0.5391</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0849</v>
+        <v>-0.7572</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4967</v>
+        <v>-0.6653</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5816</v>
+        <v>-0.092</v>
       </c>
       <c r="P17" t="n">
         <v>0.8214</v>
@@ -1780,22 +1780,22 @@
         <v>0.8214</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9399</v>
+        <v>0.7583</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6587</v>
+        <v>0.8639</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2812</v>
+        <v>-0.1055</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3491</v>
+        <v>0.9384</v>
       </c>
       <c r="W17" t="n">
-        <v>0.4805</v>
+        <v>1.1786</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8295</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3066</v>
+        <v>0.7261</v>
       </c>
       <c r="E18" t="n">
-        <v>4.0595</v>
+        <v>3.0135</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.7529</v>
+        <v>-2.2873</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6153</v>
@@ -1858,13 +1858,13 @@
         <v>2.0534</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1006</v>
+        <v>0.5201</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7432</v>
+        <v>0.6972</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-0.1771</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3509</v>
+        <v>-0.0075</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2792</v>
+        <v>0.593</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6301</v>
+        <v>-0.6004</v>
       </c>
       <c r="G19" t="n">
         <v>-0.332</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2592</v>
+        <v>0.0843</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.3138</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2592</v>
+        <v>-0.2295</v>
       </c>
       <c r="V19" t="n">
         <v>0.2402</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5945</v>
+        <v>-0.8438</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6921</v>
+        <v>-3.1105</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0976</v>
+        <v>2.2667</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1951</v>
@@ -2014,13 +2014,13 @@
         <v>2.4641</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1201</v>
+        <v>0.8708</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1117</v>
+        <v>0.6933</v>
       </c>
       <c r="U20" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.1775</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6982</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4367</v>
+        <v>-3.8098</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.15</v>
+        <v>-1.4638</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2867</v>
+        <v>-2.346</v>
       </c>
       <c r="G21" t="n">
         <v>-3.466</v>
@@ -2092,13 +2092,13 @@
         <v>1.0267</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3866</v>
+        <v>0.0135</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9336</v>
+        <v>0.6198</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.547</v>
+        <v>-0.6063</v>
       </c>
       <c r="V21" t="n">
         <v>-1.1786</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. FANER CATALA</t>
+          <t>O. RUSSELL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9659</v>
+        <v>-3.8773</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.9191</v>
+        <v>-3.693</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0468</v>
+        <v>-0.1843</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3232</v>
+        <v>-2.3331</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4347</v>
+        <v>-0.4702</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7579</v>
+        <v>-1.8629</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3811</v>
+        <v>-1.395</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2103</v>
+        <v>0.0526</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-1.4476</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7044</v>
+        <v>-0.9381</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7756</v>
+        <v>-0.5228</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0713</v>
+        <v>-0.4154</v>
       </c>
       <c r="P22" t="n">
-        <v>-4.3122</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.3389</v>
+        <v>-2.2588</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0267</v>
+        <v>2.0534</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3305</v>
+        <v>-0.0513</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0386</v>
+        <v>-0.1707</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3691</v>
+        <v>0.1193</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.2875</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.1314</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>O. RUSSELL</t>
+          <t>J. FANER CATALA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9669</v>
+        <v>-4.4446</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.6344</v>
+        <v>-4.6053</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3325</v>
+        <v>0.1607</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.3331</v>
+        <v>-0.3232</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4702</v>
+        <v>0.4347</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.8629</v>
+        <v>-0.7579</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.395</v>
+        <v>0.3811</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0526</v>
+        <v>1.2103</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.4476</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9381</v>
+        <v>-0.7044</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5228</v>
+        <v>-0.7756</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4154</v>
+        <v>0.0713</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2053</v>
+        <v>-4.3122</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2588</v>
+        <v>-5.3389</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0534</v>
+        <v>1.0267</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.141</v>
+        <v>0.1908</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1121</v>
+        <v>0.3524</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0289</v>
+        <v>-0.1616</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2875</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1314</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>7.857599999999997</v>
+        <v>8.554800000000004</v>
       </c>
       <c r="E24" t="n">
-        <v>8.901899999999998</v>
+        <v>8.901999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0444</v>
+        <v>-0.3469000000000002</v>
       </c>
       <c r="G24" t="n">
         <v>4.736</v>
@@ -2317,7 +2317,7 @@
         <v>-1.8394</v>
       </c>
       <c r="P24" t="n">
-        <v>0.0001999999999997837</v>
+        <v>0.0001999999999995339</v>
       </c>
       <c r="Q24" t="n">
         <v>-14.374</v>
@@ -2326,13 +2326,13 @@
         <v>14.374</v>
       </c>
       <c r="S24" t="n">
-        <v>3.448200000000001</v>
+        <v>4.1455</v>
       </c>
       <c r="T24" t="n">
         <v>3.621</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1727999999999995</v>
+        <v>0.5246000000000002</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3266000000000002</v>
